--- a/generated_outputs/Weekly Schedules.xlsx
+++ b/generated_outputs/Weekly Schedules.xlsx
@@ -431,7 +431,7 @@
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lab 1: Lab 1 in-lab activity</t>
+          <t>Lab 1: Completed `lab-starter.R` with the requested objects and plots. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lab 2: Tutorial 2 hash | Lab 2 in-lab activity</t>
+          <t>Lab 2: Completed `lab-starter.R` with the fitted models and requested autograder objects. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Project1-1: Project 1 outline</t>
+          <t>Project1-1: Completed Project 1 outline submitted through the course platform. | Shared Google Doc containing the title, motivation, questions, data description, limitations, roles, and timeline.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Project1-2: Project 1 plan</t>
+          <t>Project1-2: Project 1 progress materials submitted through the course platform. | Cleaned-data notes, initial EDA, revised questions, and accessible shared Google Doc link.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Project1-3: Project 1 progress report</t>
+          <t>Project1-3: Project 1 progress report submitted through the course platform. | Candidate models, diagnostics, justified modeling direction, and accessible shared Google Doc link.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Project1-4: Project 1 video</t>
+          <t>Project1-4: Project 1 final presentation materials or video submitted through the course platform. | Shared script/document link and reproducible supporting files.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -692,7 +692,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Project2-1: Project 2 initial plan</t>
+          <t>Project2-1: Completed Project 2 outline submitted through the course platform. | Shared document with study plans, research questions, real-data plan, timeline, roles, and planned outputs.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Project2-2: Project 2 plan</t>
+          <t>Project2-2: Project 2 simulation-design materials submitted through the course platform. | Simulation algorithm, planned outputs, shared document link, and reproducible code files.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Project2-3: Project 2 progress report</t>
+          <t>Project2-3: Project 2 progress report submitted through the course platform. | Real-data analysis, diagnostics, shared document link, and reproducible code files.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Project2-4: Project 2 write-up</t>
+          <t>Project2-4: Project 2 writeup, code, and required supporting files submitted through the course platform. | Shared Google Doc link and confirmation of group review.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lab 3: Tutorial 3 hash</t>
+          <t>Lab 3: Completed `lab-starter.R` with the required posterior objects. | Completed posterior-probability practice or Tutorial 3 hash, as assigned.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lab 4: Tutorial 4 hash</t>
+          <t>Lab 4: Completed `lab-starter.R` with the requested posterior summaries. | Completed conjugate-model practice or Tutorial 4 hash, as assigned.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lab 5: Tutorial 5 hash</t>
+          <t>Lab 5: Completed `lab-starter.R` with the data, log-posterior, credible interval, and posterior predictive mean objects. | Completed Bayesian-regression practice or Tutorial 5 hash, as assigned.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>

--- a/generated_outputs/Weekly Schedules.xlsx
+++ b/generated_outputs/Weekly Schedules.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lab 1: Completed `lab-starter.R` with the requested objects and plots. | Completed in-lab activity response sheet.</t>
+          <t>Lab 1: Tutorial 1 hash submitted before lab. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lab 2: Completed `lab-starter.R` with the fitted models and requested autograder objects. | Completed in-lab activity response sheet.</t>
+          <t>Lab 2: Tutorial 2 hash submitted before lab. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lab 3: Completed `lab-starter.R` with the required posterior objects. | Completed posterior-probability practice or Tutorial 3 hash, as assigned.</t>
+          <t>Lab 3: Tutorial 3 hash submitted before lab. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lab 4: Completed `lab-starter.R` with the requested posterior summaries. | Completed conjugate-model practice or Tutorial 4 hash, as assigned.</t>
+          <t>Lab 4: Tutorial 4 hash submitted before lab. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lab 5: Completed `lab-starter.R` with the data, log-posterior, credible interval, and posterior predictive mean objects. | Completed Bayesian-regression practice or Tutorial 5 hash, as assigned.</t>
+          <t>Lab 5: Tutorial 5 hash submitted before lab. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>

--- a/generated_outputs/Weekly Schedules.xlsx
+++ b/generated_outputs/Weekly Schedules.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lab 1: Tutorial 1 hash submitted before lab. | Completed in-lab activity response sheet.</t>
+          <t>Lab 1: Tutorial 1 hash (due before lab). | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lab 2: Tutorial 2 hash submitted before lab. | Completed in-lab activity response sheet.</t>
+          <t>Lab 2: Tutorial 2 hash (due before lab). | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lab 3: Tutorial 3 hash submitted before lab. | Completed in-lab activity response sheet.</t>
+          <t>Lab 3: Tutorial 3 hash (due before lab). | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lab 4: Tutorial 4 hash submitted before lab. | Completed in-lab activity response sheet.</t>
+          <t>Lab 4: Tutorial 4 hash (due before lab). | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lab 5: Tutorial 5 hash submitted before lab. | Completed in-lab activity response sheet.</t>
+          <t>Lab 5: Tutorial 5 hash (due before lab). | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>

--- a/generated_outputs/Weekly Schedules.xlsx
+++ b/generated_outputs/Weekly Schedules.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lab 1: Tutorial 1 hash (due before lab). | Completed in-lab activity response sheet.</t>
+          <t>Lab 1: Tutorial 1 hash. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lab 2: Tutorial 2 hash (due before lab). | Completed in-lab activity response sheet.</t>
+          <t>Lab 2: Tutorial 2 hash. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lab 3: Tutorial 3 hash (due before lab). | Completed in-lab activity response sheet.</t>
+          <t>Lab 3: Tutorial 3 hash. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lab 4: Tutorial 4 hash (due before lab). | Completed in-lab activity response sheet.</t>
+          <t>Lab 4: Tutorial 4 hash. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lab 5: Tutorial 5 hash (due before lab). | Completed in-lab activity response sheet.</t>
+          <t>Lab 5: Tutorial 5 hash. | Completed in-lab activity response sheet.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
